--- a/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Damien aide papa dans la cuisine. Papa range le pain. Sur la table, il y a un petit pot. Damien ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Damien va vers papa. Papa, c'est l'adulte. Damien dit : je demande. Papa prend le pot. Papa dit : merci d'avoir demandé. L'inconnu, on le montre à un adulte. Plus tard, au jardin, Damien voit une baie. Il ne la connaît pas. C'est inconnu. Il demande à l'adulte. Papa vient. Damien a les pieds au sol, près de papa.</t>
+          <t>Damien aide papa dans la cuisine. Papa range le pain. Sur la table, il y a un petit pot. Damien ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Damien va vers papa. Papa, c'est l'adulte. Je demande. Papa prend le pot. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Plus tard, au jardin, Damien voit une baie. Il ne la connaît pas. C'est inconnu. Il demande à l'adulte. Papa vient. Damien a les pieds au sol, près de papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Damien aide papa dans la cuisine. Papa range le pain. Sur la table, il y a un petit pot. Damien ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Damien va vers papa. Papa, c'est l'adulte.
+enfant-m|Je demande. Papa prend le pot.
+papa|Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Plus tard, au jardin, Damien voit une baie. Il ne la connaît pas. C'est inconnu. Il demande à l'adulte. Papa vient.
+narrateur|Damien a les pieds au sol, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Damien voit quelque chose d'inconnu. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1645,6 +1674,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Damien a demandé. L'inconnu, on le montre à un adulte. Papa a écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1841,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Damien pose une serviette. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2008,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2048,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Damien a les pieds au sol, près de papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Damien voit quelque chose d'inconnu. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1679,6 +1686,7 @@
           <t>narrateur|Damien a demandé. L'inconnu, on le montre à un adulte. Papa a écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1846,6 +1854,7 @@
           <t>narrateur|Damien pose une serviette. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2013,6 +2022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2055,6 +2065,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2280,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Damien demande avant l'inconnu</t>
+          <t>Le pain d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les bottes font une flaque. Aniss aide papa au pain. Un petit pot inconnu attend. Il demande. Au jardin, une feuille brille. Il demande encore.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Damien aide papa dans la cuisine. Papa range le pain. Sur la table, il y a un petit pot. Damien ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Damien va vers papa. Papa, c'est l'adulte. Je demande. Papa prend le pot. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Plus tard, au jardin, Damien voit une baie. Il ne la connaît pas. C'est inconnu. Il demande à l'adulte. Papa vient. Damien a les pieds au sol, près de papa.</t>
+          <t>Les bottes mouillées font une petite flaque. Elle brille près du paillasson. La pluie tape encore sur le zinc. Ça fait un bruit doux, tout régulier. Dans la cuisine, la farine est blanche. Elle fait un nuage sur la planche. Un grain de farine colle au bois. Papa range le pain chaud. Ça sent le four, encore tiède. Tu as vu la farine, Aniss ? Oui, papa. Elle est blanche. Tes bottes restent près de la porte. La flaque sèche toute seule. En ce moment, Aniss aide papa. Il pose une petite assiette. L'assiette est ronde et froide. Bravo. Elle est bien posée. Sur la table, il y a un petit pot. Le couvercle est gris. Aniss ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, c'est l'adulte. Je demande. Je ne connais pas. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Papa prend le petit pot. Il le pose près de lui. Tu as bien demandé, Aniss. C'est du bon travail. J'ai demandé à l'adulte. Oui. On peut demander. Demander à l'adulte. Demander. Tu as fini de poser l'assiette ? Oui, papa. Bravo. Plus tard, au jardin, l'herbe est mouillée. Une goutte pend à une feuille. La feuille brille, toute verte. Aniss ne la connaît pas. C'est inconnu. Ses mains restent près de lui. Il demande à l'adulte. Papa, je demande. Je viens. Papa vient près de lui. Aniss reste près de papa. Tu as encore demandé. Bravo, Aniss. L'inconnu, on le montre. Oui. À un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,71 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Damien aide papa dans la cuisine. Papa range le pain. Sur la table, il y a un petit pot. Damien ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Damien va vers papa. Papa, c'est l'adulte.
-enfant-m|Je demande. Papa prend le pot.
-papa|Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Plus tard, au jardin, Damien voit une baie. Il ne la connaît pas. C'est inconnu. Il demande à l'adulte. Papa vient.
-narrateur|Damien a les pieds au sol, près de papa.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les bottes mouillées font une petite flaque.
+narrateur|Elle brille près du paillasson.
+narrateur|La pluie tape encore sur le zinc.
+narrateur|Ça fait un bruit doux, tout régulier.
+narrateur|Dans la cuisine, la farine est blanche.
+narrateur|Elle fait un nuage sur la planche.
+narrateur|Un grain de farine colle au bois.
+narrateur|Papa range le pain chaud.
+narrateur|Ça sent le four, encore tiède.
+papa|Tu as vu la farine, Aniss ?
+enfant-m|Oui, papa.
+enfant-m|Elle est blanche.
+maman|Tes bottes restent près de la porte.
+maman|La flaque sèche toute seule.
+narrateur|En ce moment, Aniss aide papa.
+narrateur|Il pose une petite assiette.
+narrateur|L'assiette est ronde et froide.
+papa|Bravo.
+papa|Elle est bien posée.
+narrateur|Sur la table, il y a un petit pot.
+narrateur|Le couvercle est gris.
+narrateur|Aniss ne le connaît pas.
+narrateur|C'est inconnu.
+narrateur|Ses mains restent près de lui.
+narrateur|Il va vers papa.
+narrateur|Papa, c'est l'adulte.
+enfant-m|Je demande.
+enfant-m|Je ne connais pas.
+papa|Merci d'avoir demandé.
+papa|L'inconnu, on le montre à un adulte.
+narrateur|Papa prend le petit pot.
+narrateur|Il le pose près de lui.
+maman|Tu as bien demandé, Aniss.
+maman|C'est du bon travail.
+enfant-m|J'ai demandé à l'adulte.
+papa|Oui.
+papa|On peut demander.
+papa|Demander à l'adulte.
+enfant-m|Demander.
+papa|Tu as fini de poser l'assiette ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Plus tard, au jardin, l'herbe est mouillée.
+narrateur|Une goutte pend à une feuille.
+narrateur|La feuille brille, toute verte.
+narrateur|Aniss ne la connaît pas.
+narrateur|C'est inconnu.
+narrateur|Ses mains restent près de lui.
+narrateur|Il demande à l'adulte.
+enfant-m|Papa, je demande.
+papa|Je viens.
+narrateur|Papa vient près de lui.
+narrateur|Aniss reste près de papa.
+maman|Tu as encore demandé.
+maman|Bravo, Aniss.
+enfant-m|L'inconnu, on le montre.
+papa|Oui.
+papa|À un adulte.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie,porte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Damien voit quelque chose d'inconnu. Que fait-il ?</t>
+          <t>Aniss voit quelque chose d'inconnu. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1577,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Damien voit quelque chose d'inconnu. Que fait-il ?</t>
+          <t>narrateur|Aniss voit quelque chose d'inconnu.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Damien a demandé. L'inconnu, on le montre à un adulte. Papa a écouté.</t>
+          <t>Aniss a demandé. L'inconnu, on le montre à un adulte. Papa a écouté. Merci d'avoir demandé. Bravo, Aniss. J'ai demandé. Oui. C'est du bon travail. On demande à l'adulte, d'accord ? D'accord.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1683,7 +1754,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Damien a demandé. L'inconnu, on le montre à un adulte. Papa a écouté.</t>
+          <t>narrateur|Aniss a demandé.
+narrateur|L'inconnu, on le montre à un adulte.
+narrateur|Papa a écouté.
+maman|Merci d'avoir demandé.
+papa|Bravo, Aniss.
+enfant-m|J'ai demandé.
+maman|Oui.
+maman|C'est du bon travail.
+papa|On demande à l'adulte, d'accord ?
+enfant-m|D'accord.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1711,7 +1791,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Damien pose une serviette. Papa sourit.</t>
+          <t>Aniss pose une serviette près du pain. Le pain est encore tiède. Tu veux une petite part ? Oui, maman. Les mains restent près de toi. Tu as fini de ranger l'assiette ? Oui, papa. Bravo. Dehors, la pluie est plus douce. La flaque des bottes est presque sèche. Le pain sent encore le four. Tu as fait du bon travail. On a demandé, tous les deux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1851,7 +1931,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Damien pose une serviette. Papa sourit.</t>
+          <t>narrateur|Aniss pose une serviette près du pain.
+narrateur|Le pain est encore tiède.
+maman|Tu veux une petite part ?
+enfant-m|Oui, maman.
+papa|Les mains restent près de toi.
+papa|Tu as fini de ranger l'assiette ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Dehors, la pluie est plus douce.
+narrateur|La flaque des bottes est presque sèche.
+narrateur|Le pain sent encore le four.
+maman|Tu as fait du bon travail.
+papa|On a demandé, tous les deux.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1879,7 +1971,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai demandé. Papa a pris le petit pot. Bravo. Tu as fait du bon travail. Le pain tiède attend encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2019,7 +2111,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai demandé.
+enfant-m|Papa a pris le petit pot.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le pain tiède attend encore.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2041,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2079,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les bottes mouillées font une petite flaque. Elle brille près du paillasson. La pluie tape encore sur le zinc. Ça fait un bruit doux, tout régulier. Dans la cuisine, la farine est blanche. Elle fait un nuage sur la planche. Un grain de farine colle au bois. Papa range le pain chaud. Ça sent le four, encore tiède. Tu as vu la farine, Aniss ? Oui, papa. Elle est blanche. Tes bottes restent près de la porte. La flaque sèche toute seule. En ce moment, Aniss aide papa. Il pose une petite assiette. L'assiette est ronde et froide. Bravo. Elle est bien posée. Sur la table, il y a un petit pot. Le couvercle est gris. Aniss ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, c'est l'adulte. Je demande. Je ne connais pas. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Papa prend le petit pot. Il le pose près de lui. Tu as bien demandé, Aniss. C'est du bon travail. J'ai demandé à l'adulte. Oui. On peut demander. Demander à l'adulte. Demander. Tu as fini de poser l'assiette ? Oui, papa. Bravo. Plus tard, au jardin, l'herbe est mouillée. Une goutte pend à une feuille. La feuille brille, toute verte. Aniss ne la connaît pas. C'est inconnu. Ses mains restent près de lui. Il demande à l'adulte. Papa, je demande. Je viens. Papa vient près de lui. Aniss reste près de papa. Tu as encore demandé. Bravo, Aniss. L'inconnu, on le montre. Oui. À un adulte.</t>
+          <t>Les bottes mouillées font une petite flaque. Elle brille près du paillasson. La pluie tape encore sur le zinc. Ça fait un bruit doux, tout régulier. Dans la cuisine, la farine est blanche. Elle fait un nuage sur la planche. Un grain de farine colle au bois. Papa range le pain chaud. Ça sent le four, encore tiède. Tu as vu la farine, Aniss ? Oui, papa. Elle est blanche. Tes bottes restent près de la porte. La flaque sèche toute seule. En ce moment, Aniss aide papa. Il pose une petite assiette. L'assiette est ronde et froide. Bravo. Elle est bien posée. Sur la table, il y a un petit pot. Le couvercle est gris. Aniss ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, c'est l'adulte. Je demande. Je ne connais pas. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Papa prend le petit pot. Il le pose près de lui. Tu as bien demandé, Aniss. J'ai demandé à l'adulte. Oui. On peut demander. Demander à l'adulte. Demander. Tu as fini de poser l'assiette ? Oui, papa. Bravo. Plus tard, au jardin, l'herbe est mouillée. Une goutte pend à une feuille. La feuille brille, toute verte. Aniss ne la connaît pas. C'est inconnu. Ses mains restent près de lui. Il demande à l'adulte. Papa, je demande. Je viens. Papa vient près de lui. Aniss reste près de papa. Tu as encore demandé. Bravo, Aniss. L'inconnu, on le montre. Oui. À un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Damien aide papa dans la cuisine. Papa range le pain. Sur la table, il y a un petit pot. Damien ne le connaît pas. C'est &lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;. Ses mains restent près de lui. Damien va vers papa. Papa, c'est l'adulte. Damien dit : je demande. Papa prend le pot. Papa dit : merci d'avoir demandé. L'inconnu, on le montre à un adulte. Plus tard, au jardin, Damien voit une baie. Il ne la connaît pas. C'est inconnu. Il demande à l'adulte. Papa vient. Damien a les pieds au sol, près de papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les bottes mouillées font une petite flaque. Elle brille près du paillasson. La pluie tape encore sur le zinc. Ça fait un bruit doux, tout régulier. Dans la cuisine, la farine est blanche. Elle fait un nuage sur la planche. Un grain de farine colle au bois. Papa range le pain chaud. Ça sent le four, encore tiède. Tu as vu la farine, Aniss ? Oui, papa. Elle est blanche. Tes bottes restent près de la porte. La flaque sèche toute seule. En ce moment, Aniss aide papa. Il pose une petite assiette. L'assiette est ronde et froide. Bravo. Elle est bien posée. Sur la table, il y a un petit pot. Le couvercle est gris. Aniss ne le connaît pas. C'est inconnu. Ses mains restent près de lui. Il va vers papa. Papa, c'est l'adulte. Je demande. Je ne connais pas. Merci d'avoir demandé. L'inconnu, on le montre à un adulte. Papa prend le petit pot. Il le pose près de lui. Tu as bien demandé, Aniss. J'ai demandé à l'adulte. Oui. On peut demander. Demander à l'adulte. Demander. Tu as fini de poser l'assiette ? Oui, papa. Bravo. Plus tard, au jardin, l'herbe est mouillée. Une goutte pend à une feuille. La feuille brille, toute verte. Aniss ne la connaît pas. C'est inconnu. Ses mains restent près de lui. Il demande à l'adulte. Papa, je demande. Je viens. Papa vient près de lui. Aniss reste près de papa. Tu as encore demandé. Bravo, Aniss. L'inconnu, on le montre. Oui. À un adulte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1357,7 +1357,6 @@
 narrateur|Papa prend le petit pot.
 narrateur|Il le pose près de lui.
 maman|Tu as bien demandé, Aniss.
-maman|C'est du bon travail.
 enfant-m|J'ai demandé à l'adulte.
 papa|Oui.
 papa|On peut demander.
@@ -1418,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Damien voit quelque chose d'&lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss voit quelque chose d'inconnu. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1581,7 +1580,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1606,12 +1604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a demandé. L'inconnu, on le montre à un adulte. Papa a écouté. Merci d'avoir demandé. Bravo, Aniss. J'ai demandé. Oui. C'est du bon travail. On demande à l'adulte, d'accord ? D'accord.</t>
+          <t>Aniss a demandé. L'inconnu, on le montre à un adulte. Papa a écouté. Merci d'avoir demandé. Bravo, Aniss. J'ai demandé. Oui. On demande à l'adulte, d'accord ? D'accord.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Damien a demandé. L'&lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;, on le montre à un adulte. Papa a écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a demandé. L'inconnu, on le montre à un adulte. Papa a écouté. Merci d'avoir demandé. Bravo, Aniss. J'ai demandé. Oui. On demande à l'adulte, d'accord ? D'accord.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1761,12 +1759,10 @@
 papa|Bravo, Aniss.
 enfant-m|J'ai demandé.
 maman|Oui.
-maman|C'est du bon travail.
 papa|On demande à l'adulte, d'accord ?
 enfant-m|D'accord.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,12 +1787,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aniss pose une serviette près du pain. Le pain est encore tiède. Tu veux une petite part ? Oui, maman. Les mains restent près de toi. Tu as fini de ranger l'assiette ? Oui, papa. Bravo. Dehors, la pluie est plus douce. La flaque des bottes est presque sèche. Le pain sent encore le four. Tu as fait du bon travail. On a demandé, tous les deux.</t>
+          <t>Aniss pose une serviette près du pain. Le pain est encore tiède. Tu veux une petite part ? Oui, maman. Les mains restent près de toi. Tu as fini de ranger l'assiette ? Oui, papa. Bravo. Dehors, la pluie est plus douce. La flaque des bottes est presque sèche. Le pain sent encore le four. On a demandé, tous les deux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Damien pose une serviette. Papa sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss pose une serviette près du pain. Le pain est encore tiède. Tu veux une petite part ? Oui, maman. Les mains restent près de toi. Tu as fini de ranger l'assiette ? Oui, papa. Bravo. Dehors, la pluie est plus douce. La flaque des bottes est presque sèche. Le pain sent encore le four. On a demandé, tous les deux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,11 +1938,9 @@
 narrateur|Dehors, la pluie est plus douce.
 narrateur|La flaque des bottes est presque sèche.
 narrateur|Le pain sent encore le four.
-maman|Tu as fait du bon travail.
 papa|On a demandé, tous les deux.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1971,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai demandé. Papa a pris le petit pot. Bravo. Tu as fait du bon travail. Le pain tiède attend encore. L'histoire est finie.</t>
+          <t>J'ai demandé. Papa a pris le petit pot. Bravo. Le pain tiède attend encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai demandé. Papa a pris le petit pot. Bravo. Le pain tiède attend encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,12 +2108,9 @@
           <t>enfant-m|J'ai demandé.
 enfant-m|Papa a pris le petit pot.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le pain tiède attend encore.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le pain tiède attend encore.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2138,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2174,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Damien, papa</t>
+          <t>Aniss, papa, maman</t>
         </is>
       </c>
     </row>
